--- a/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.B. ZARAGOZA.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.B. ZARAGOZA.xlsx
@@ -565,13 +565,13 @@
         <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>36.3408</v>
+        <v>51.639</v>
       </c>
       <c r="E2" t="n">
-        <v>33.2677</v>
+        <v>42.415</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0732</v>
+        <v>9.224399999999999</v>
       </c>
       <c r="G2" t="n">
         <v>38.2211</v>
@@ -610,13 +610,13 @@
         <v>47.4342</v>
       </c>
       <c r="S2" t="n">
-        <v>-18.6028</v>
+        <v>-3.3043</v>
       </c>
       <c r="T2" t="n">
-        <v>-11.6822</v>
+        <v>-2.5348</v>
       </c>
       <c r="U2" t="n">
-        <v>-6.9207</v>
+        <v>-0.7694999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>23.293</v>
@@ -643,13 +643,13 @@
         <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>26.8145</v>
+        <v>41.0871</v>
       </c>
       <c r="E3" t="n">
-        <v>34.349</v>
+        <v>43.5619</v>
       </c>
       <c r="F3" t="n">
-        <v>-7.5345</v>
+        <v>-2.475000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>46.2895</v>
@@ -688,13 +688,13 @@
         <v>42.9165</v>
       </c>
       <c r="S3" t="n">
-        <v>-18.0557</v>
+        <v>-3.7829</v>
       </c>
       <c r="T3" t="n">
-        <v>-14.099</v>
+        <v>-4.8861</v>
       </c>
       <c r="U3" t="n">
-        <v>-3.9568</v>
+        <v>1.1031</v>
       </c>
       <c r="V3" t="n">
         <v>-10.4546</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. GATELL SANZ</t>
+          <t>D. ARJOL LOPEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>14.8215</v>
+        <v>11.677</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3332000000000002</v>
+        <v>1.059200000000002</v>
       </c>
       <c r="F4" t="n">
-        <v>15.1543</v>
+        <v>10.618</v>
       </c>
       <c r="G4" t="n">
-        <v>21.8612</v>
+        <v>20.932</v>
       </c>
       <c r="H4" t="n">
-        <v>17.3471</v>
+        <v>24.5839</v>
       </c>
       <c r="I4" t="n">
-        <v>4.5138</v>
+        <v>-3.6521</v>
       </c>
       <c r="J4" t="n">
-        <v>34.0793</v>
+        <v>51.3889</v>
       </c>
       <c r="K4" t="n">
-        <v>21.7274</v>
+        <v>39.7137</v>
       </c>
       <c r="L4" t="n">
-        <v>12.3519</v>
+        <v>11.6759</v>
       </c>
       <c r="M4" t="n">
-        <v>-12.2185</v>
+        <v>-30.4572</v>
       </c>
       <c r="N4" t="n">
-        <v>-4.380199999999999</v>
+        <v>-15.1293</v>
       </c>
       <c r="O4" t="n">
-        <v>-7.838100000000001</v>
+        <v>-15.3276</v>
       </c>
       <c r="P4" t="n">
-        <v>-6.981699999999999</v>
+        <v>-17.4538</v>
       </c>
       <c r="Q4" t="n">
-        <v>-48.0498</v>
+        <v>-62.4241</v>
       </c>
       <c r="R4" t="n">
-        <v>41.0686</v>
+        <v>44.9699</v>
       </c>
       <c r="S4" t="n">
-        <v>16.0777</v>
+        <v>-2.9719</v>
       </c>
       <c r="T4" t="n">
-        <v>4.4899</v>
+        <v>-4.1927</v>
       </c>
       <c r="U4" t="n">
-        <v>11.5881</v>
+        <v>1.2208</v>
       </c>
       <c r="V4" t="n">
-        <v>-16.136</v>
+        <v>11.1716</v>
       </c>
       <c r="W4" t="n">
-        <v>9.147500000000001</v>
+        <v>16.2869</v>
       </c>
       <c r="X4" t="n">
-        <v>-25.2835</v>
+        <v>-5.1155</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>14.4332</v>
+        <v>11.0888</v>
       </c>
       <c r="E5" t="n">
-        <v>6.9723</v>
+        <v>2.8737</v>
       </c>
       <c r="F5" t="n">
-        <v>7.4605</v>
+        <v>8.215400000000001</v>
       </c>
       <c r="G5" t="n">
         <v>-2.8472</v>
@@ -844,13 +844,13 @@
         <v>30.8015</v>
       </c>
       <c r="S5" t="n">
-        <v>5.4394</v>
+        <v>2.0953</v>
       </c>
       <c r="T5" t="n">
-        <v>3.4605</v>
+        <v>-0.6386999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>1.9792</v>
+        <v>2.7345</v>
       </c>
       <c r="V5" t="n">
         <v>-8.2826</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Y. KOLO</t>
+          <t>E. GATELL SANZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>7.209700000000001</v>
+        <v>2.788500000000002</v>
       </c>
       <c r="E6" t="n">
-        <v>8.5061</v>
+        <v>-5.636700000000002</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2963</v>
+        <v>8.425200000000002</v>
       </c>
       <c r="G6" t="n">
-        <v>4.7541</v>
+        <v>21.8612</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.1849</v>
+        <v>17.3471</v>
       </c>
       <c r="I6" t="n">
-        <v>6.939100000000001</v>
+        <v>4.5138</v>
       </c>
       <c r="J6" t="n">
-        <v>19.4721</v>
+        <v>34.0793</v>
       </c>
       <c r="K6" t="n">
-        <v>13.0024</v>
+        <v>21.7274</v>
       </c>
       <c r="L6" t="n">
-        <v>6.469399999999999</v>
+        <v>12.3519</v>
       </c>
       <c r="M6" t="n">
-        <v>-14.718</v>
+        <v>-12.2185</v>
       </c>
       <c r="N6" t="n">
-        <v>-15.1874</v>
+        <v>-4.380199999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4696999999999999</v>
+        <v>-7.838100000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.2855</v>
+        <v>-6.981699999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>-20.9448</v>
+        <v>-48.0498</v>
       </c>
       <c r="R6" t="n">
-        <v>17.6594</v>
+        <v>41.0686</v>
       </c>
       <c r="S6" t="n">
-        <v>12.1312</v>
+        <v>4.045</v>
       </c>
       <c r="T6" t="n">
-        <v>4.9567</v>
+        <v>-0.8134999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>7.1745</v>
+        <v>4.8589</v>
       </c>
       <c r="V6" t="n">
-        <v>-6.390200000000001</v>
+        <v>-16.136</v>
       </c>
       <c r="W6" t="n">
-        <v>5.0223</v>
+        <v>9.147500000000001</v>
       </c>
       <c r="X6" t="n">
-        <v>-11.4123</v>
+        <v>-25.2835</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. MUÑOZ SAMATAN</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4.749199999999998</v>
+        <v>2.3988</v>
       </c>
       <c r="E7" t="n">
-        <v>30.7983</v>
+        <v>1.7904</v>
       </c>
       <c r="F7" t="n">
-        <v>-26.0494</v>
+        <v>0.6085</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3933</v>
+        <v>1.4893</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9431</v>
+        <v>0.3211</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.3364</v>
+        <v>1.1683</v>
       </c>
       <c r="J7" t="n">
-        <v>28.7549</v>
+        <v>2.0151</v>
       </c>
       <c r="K7" t="n">
-        <v>18.1402</v>
+        <v>1.2653</v>
       </c>
       <c r="L7" t="n">
-        <v>10.6147</v>
+        <v>0.7498</v>
       </c>
       <c r="M7" t="n">
-        <v>-30.1482</v>
+        <v>-0.5258</v>
       </c>
       <c r="N7" t="n">
-        <v>-16.197</v>
+        <v>-0.9442</v>
       </c>
       <c r="O7" t="n">
-        <v>-13.9512</v>
+        <v>0.4184</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.0266</v>
+        <v>1.0267</v>
       </c>
       <c r="Q7" t="n">
-        <v>-32.0332</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>31.0066</v>
+        <v>1.0267</v>
       </c>
       <c r="S7" t="n">
-        <v>15.6146</v>
+        <v>-0.1172</v>
       </c>
       <c r="T7" t="n">
-        <v>24.1633</v>
+        <v>-0.2248</v>
       </c>
       <c r="U7" t="n">
-        <v>-8.548499999999999</v>
+        <v>0.1075</v>
       </c>
       <c r="V7" t="n">
-        <v>-8.445500000000001</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>9.9131</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-18.3586</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>Y. KOLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>2.146</v>
+        <v>1.0713</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6858</v>
+        <v>4.326000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4603</v>
+        <v>-3.2546</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4893</v>
+        <v>4.7541</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3211</v>
+        <v>-2.1849</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1683</v>
+        <v>6.939100000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>2.0151</v>
+        <v>19.4721</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2653</v>
+        <v>13.0024</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7498</v>
+        <v>6.469399999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5258</v>
+        <v>-14.718</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9442</v>
+        <v>-15.1874</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4184</v>
+        <v>0.4696999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0267</v>
+        <v>-3.2855</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-20.9448</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0267</v>
+        <v>17.6594</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.37</v>
+        <v>5.9928</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3294</v>
+        <v>0.7765999999999997</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0407</v>
+        <v>5.216</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-6.390200000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>5.0223</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-11.4123</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. ARJOL LOPEZ</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.799300000000001</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.244199999999998</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>8.042899999999999</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>20.932</v>
+        <v>0.1395</v>
       </c>
       <c r="H9" t="n">
-        <v>24.5839</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.6521</v>
+        <v>0.1395</v>
       </c>
       <c r="J9" t="n">
-        <v>51.3889</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>39.7137</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>11.6759</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-30.4572</v>
+        <v>0.1395</v>
       </c>
       <c r="N9" t="n">
-        <v>-15.1293</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-15.3276</v>
+        <v>0.1395</v>
       </c>
       <c r="P9" t="n">
-        <v>-17.4538</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-62.4241</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>44.9699</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-12.8499</v>
+        <v>-0.1395</v>
       </c>
       <c r="T9" t="n">
-        <v>-11.4958</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.3545</v>
+        <v>-0.1395</v>
       </c>
       <c r="V9" t="n">
-        <v>11.1716</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>16.2869</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-5.1155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,22 +1189,22 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-0.3947</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-0.3947</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1395</v>
+        <v>-0.3947</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1395</v>
+        <v>-0.3947</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1216,13 +1216,13 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1395</v>
+        <v>-0.3947</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1395</v>
+        <v>-0.3947</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1395</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1395</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>G. GEORGIOU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3947</v>
+        <v>-2.4443</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>-2.758</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3947</v>
+        <v>0.3137</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3947</v>
+        <v>-2.799</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0.8466</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3947</v>
+        <v>-1.9522</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-2.5029</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-0.6869999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-1.8158</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3947</v>
+        <v>-0.2959</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-0.1596</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3947</v>
+        <v>-0.1364</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.6160000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.232</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.8481</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-0.2615</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>-0.2017</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-0.05969999999999998</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. GEORGIOU</t>
+          <t>L. ANDRES ARENAS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5168</v>
+        <v>-2.6488</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8897</v>
+        <v>-3.0257</v>
       </c>
       <c r="F12" t="n">
-        <v>0.373</v>
+        <v>0.3769</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.799</v>
+        <v>-2.6566</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8466</v>
+        <v>-2.2382</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.9522</v>
+        <v>-0.4184</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.5029</v>
+        <v>-2.7699</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6869999999999999</v>
+        <v>-2.0726</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.8158</v>
+        <v>-0.6974</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2959</v>
+        <v>0.1134</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1596</v>
+        <v>-0.1656</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1364</v>
+        <v>0.2789</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6160000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.232</v>
+        <v>-0.2053</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8481</v>
+        <v>0.2053</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3339</v>
+        <v>0.0077</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3335</v>
+        <v>-0.0504</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0003999999999999837</v>
+        <v>0.0581</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L. ANDRES ARENAS</t>
+          <t>G. COLOM BARRUFET</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.7674</v>
+        <v>-3.3204</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.0257</v>
+        <v>-4.4423</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2583</v>
+        <v>1.122000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.6566</v>
+        <v>-4.913500000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.2382</v>
+        <v>-6.3991</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4184</v>
+        <v>1.4855</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.7699</v>
+        <v>7.789</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.0726</v>
+        <v>5.8503</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6974</v>
+        <v>1.938900000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1134</v>
+        <v>-12.7027</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1656</v>
+        <v>-12.2498</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2789</v>
+        <v>-0.4532</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.464</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.2053</v>
+        <v>-18.8913</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2053</v>
+        <v>21.3553</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1108</v>
+        <v>-6.545599999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0504</v>
+        <v>-3.3808</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0604</v>
+        <v>-3.1648</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>5.674700000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>10.0406</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-4.3659</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.493899999999999</v>
+        <v>-4.4739</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.1463</v>
+        <v>-5.3286</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6525000000000001</v>
+        <v>0.8548000000000002</v>
       </c>
       <c r="G14" t="n">
         <v>0.3309000000000006</v>
@@ -1546,13 +1546,13 @@
         <v>4.9281</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0158</v>
+        <v>-0.9957999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4461000000000002</v>
+        <v>-0.6281</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5698000000000001</v>
+        <v>-0.3676</v>
       </c>
       <c r="V14" t="n">
         <v>-1.5502</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. KNOWLES</t>
+          <t>A. ARAGONES NAVAIS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>-5.6576</v>
+        <v>-5.614000000000002</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.6417</v>
+        <v>-15.2608</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.01569999999999994</v>
+        <v>9.6465</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.5103</v>
+        <v>3.154100000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8172000000000003</v>
+        <v>5.177</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.6931</v>
+        <v>-2.0229</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4499</v>
+        <v>15.6285</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8319</v>
+        <v>13.0559</v>
       </c>
       <c r="L15" t="n">
-        <v>1.6179</v>
+        <v>2.5724</v>
       </c>
       <c r="M15" t="n">
-        <v>-5.9603</v>
+        <v>-12.4743</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.6491</v>
+        <v>-7.8789</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.3115</v>
+        <v>-4.5951</v>
       </c>
       <c r="P15" t="n">
-        <v>-5.749700000000001</v>
+        <v>-7.392300000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>-11.4991</v>
+        <v>-39.4253</v>
       </c>
       <c r="R15" t="n">
-        <v>5.7495</v>
+        <v>32.0334</v>
       </c>
       <c r="S15" t="n">
-        <v>3.0604</v>
+        <v>-0.6292</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3624</v>
+        <v>-1.5494</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6979000000000001</v>
+        <v>0.9200999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.4580000000000001</v>
+        <v>-0.7469999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>0.04489999999999997</v>
+        <v>10.0859</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5029</v>
+        <v>-10.8328</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ARAGONES NAVAIS</t>
+          <t>D. MUÑOZ SAMATAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-6.525300000000001</v>
+        <v>-6.0862</v>
       </c>
       <c r="E16" t="n">
-        <v>-14.362</v>
+        <v>15.1002</v>
       </c>
       <c r="F16" t="n">
-        <v>7.8368</v>
+        <v>-21.1866</v>
       </c>
       <c r="G16" t="n">
-        <v>3.154100000000001</v>
+        <v>-1.3933</v>
       </c>
       <c r="H16" t="n">
-        <v>5.177</v>
+        <v>1.9431</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.0229</v>
+        <v>-3.3364</v>
       </c>
       <c r="J16" t="n">
-        <v>15.6285</v>
+        <v>28.7549</v>
       </c>
       <c r="K16" t="n">
-        <v>13.0559</v>
+        <v>18.1402</v>
       </c>
       <c r="L16" t="n">
-        <v>2.5724</v>
+        <v>10.6147</v>
       </c>
       <c r="M16" t="n">
-        <v>-12.4743</v>
+        <v>-30.1482</v>
       </c>
       <c r="N16" t="n">
-        <v>-7.8789</v>
+        <v>-16.197</v>
       </c>
       <c r="O16" t="n">
-        <v>-4.5951</v>
+        <v>-13.9512</v>
       </c>
       <c r="P16" t="n">
-        <v>-7.392300000000001</v>
+        <v>-1.0266</v>
       </c>
       <c r="Q16" t="n">
-        <v>-39.4253</v>
+        <v>-32.0332</v>
       </c>
       <c r="R16" t="n">
-        <v>32.0334</v>
+        <v>31.0066</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5402</v>
+        <v>4.7796</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6502999999999997</v>
+        <v>8.465199999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8895999999999998</v>
+        <v>-3.6858</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.7469999999999999</v>
+        <v>-8.445500000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>10.0859</v>
+        <v>9.9131</v>
       </c>
       <c r="X16" t="n">
-        <v>-10.8328</v>
+        <v>-18.3586</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. COLOM BARRUFET</t>
+          <t>D. KNOWLES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>-13.4033</v>
+        <v>-7.3512</v>
       </c>
       <c r="E17" t="n">
-        <v>-10.8811</v>
+        <v>-6.556</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.522200000000001</v>
+        <v>-0.7953000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-4.913500000000001</v>
+        <v>-2.5103</v>
       </c>
       <c r="H17" t="n">
-        <v>-6.3991</v>
+        <v>-0.8172000000000003</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4855</v>
+        <v>-1.6931</v>
       </c>
       <c r="J17" t="n">
-        <v>7.789</v>
+        <v>3.4499</v>
       </c>
       <c r="K17" t="n">
-        <v>5.8503</v>
+        <v>1.8319</v>
       </c>
       <c r="L17" t="n">
-        <v>1.938900000000001</v>
+        <v>1.6179</v>
       </c>
       <c r="M17" t="n">
-        <v>-12.7027</v>
+        <v>-5.9603</v>
       </c>
       <c r="N17" t="n">
-        <v>-12.2498</v>
+        <v>-2.6491</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4532</v>
+        <v>-3.3115</v>
       </c>
       <c r="P17" t="n">
-        <v>2.464</v>
+        <v>-5.749700000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>-18.8913</v>
+        <v>-11.4991</v>
       </c>
       <c r="R17" t="n">
-        <v>21.3553</v>
+        <v>5.7495</v>
       </c>
       <c r="S17" t="n">
-        <v>-16.6287</v>
+        <v>1.3667</v>
       </c>
       <c r="T17" t="n">
-        <v>-9.819900000000001</v>
+        <v>1.4482</v>
       </c>
       <c r="U17" t="n">
-        <v>-6.8088</v>
+        <v>-0.08149999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>5.674700000000001</v>
+        <v>-0.4580000000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>10.0406</v>
+        <v>0.04489999999999997</v>
       </c>
       <c r="X17" t="n">
-        <v>-4.3659</v>
+        <v>-0.5029</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>23</v>
       </c>
       <c r="D18" t="n">
-        <v>-29.7802</v>
+        <v>-19.2511</v>
       </c>
       <c r="E18" t="n">
-        <v>-19.0734</v>
+        <v>-11.5727</v>
       </c>
       <c r="F18" t="n">
-        <v>-10.7071</v>
+        <v>-7.678399999999999</v>
       </c>
       <c r="G18" t="n">
         <v>-27.8958</v>
@@ -1858,13 +1858,13 @@
         <v>37.3721</v>
       </c>
       <c r="S18" t="n">
-        <v>-13.0286</v>
+        <v>-2.4998</v>
       </c>
       <c r="T18" t="n">
-        <v>-8.5426</v>
+        <v>-1.0418</v>
       </c>
       <c r="U18" t="n">
-        <v>-4.4862</v>
+        <v>-1.4576</v>
       </c>
       <c r="V18" t="n">
         <v>10.1175</v>
@@ -1891,13 +1891,13 @@
         <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>42.775</v>
+        <v>70.16589999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>47.98189999999999</v>
+        <v>56.54559999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-5.208100000000002</v>
+        <v>13.6208</v>
       </c>
       <c r="G19" t="n">
         <v>91.76130000000001</v>
@@ -1924,25 +1924,25 @@
         <v>-122.2059</v>
       </c>
       <c r="O19" t="n">
-        <v>-87.00369999999999</v>
+        <v>-87.00370000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>-16.4272</v>
+        <v>-16.42720000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>-376.8009</v>
+        <v>-376.8009000000001</v>
       </c>
       <c r="R19" t="n">
         <v>360.3752</v>
       </c>
       <c r="S19" t="n">
-        <v>-30.3526</v>
+        <v>-2.960599999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-18.0164</v>
+        <v>-9.4528</v>
       </c>
       <c r="U19" t="n">
-        <v>-12.3362</v>
+        <v>6.493</v>
       </c>
       <c r="V19" t="n">
         <v>-2.2073</v>
